--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.93740228165275</v>
+        <v>6.977327870768573</v>
       </c>
       <c r="D2" t="n">
-        <v>41.29371186115981</v>
+        <v>6.710228177438469</v>
       </c>
       <c r="E2" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F2" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.14893184045695</v>
+        <v>8.474201424074256</v>
       </c>
       <c r="D3" t="n">
-        <v>47.87553924820499</v>
+        <v>7.779775127833312</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F3" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.25977284079794</v>
+        <v>6.217213086629666</v>
       </c>
       <c r="D4" t="n">
-        <v>29.46820677862343</v>
+        <v>4.788583601526307</v>
       </c>
       <c r="E4" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F4" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.604850771630005</v>
+        <v>0.9107882503898759</v>
       </c>
       <c r="D5" t="n">
-        <v>4.429969545890216</v>
+        <v>0.7198700512071602</v>
       </c>
       <c r="E5" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F5" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.85076983088062</v>
+        <v>4.850750097518101</v>
       </c>
       <c r="D6" t="n">
-        <v>29.16522350097169</v>
+        <v>4.7393488189079</v>
       </c>
       <c r="E6" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F6" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.61340123305769</v>
+        <v>1.887177700371874</v>
       </c>
       <c r="D7" t="n">
-        <v>13.080827934296</v>
+        <v>2.125634539323099</v>
       </c>
       <c r="E7" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F7" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.56966494993417</v>
+        <v>5.455070554364303</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62028663432885</v>
+        <v>4.325796578078438</v>
       </c>
       <c r="E8" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F8" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>3.85072504677279</v>
+        <v>0.6257428201005785</v>
       </c>
       <c r="D9" t="n">
-        <v>4.420582690235387</v>
+        <v>0.7183446871632504</v>
       </c>
       <c r="E9" t="n">
-        <v>16.93556559668098</v>
+        <v>2.752029409460659</v>
       </c>
       <c r="F9" t="n">
-        <v>15.06551739405815</v>
+        <v>2.448146576534449</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
